--- a/Deliverables/BOM/Electrode-Board/CLient_BOM_Electrode_Board.xlsx
+++ b/Deliverables/BOM/Electrode-Board/CLient_BOM_Electrode_Board.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\ManarHarake-sEMGDevice\Deliverables\BOM\Electrode-Board\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{09F3D584-EE28-4626-88B7-18D6795E2A71}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E1384C2D-378D-433E-B345-05DC13DE3D44}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="99" uniqueCount="82">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="86">
   <si>
     <t>Component list</t>
   </si>
@@ -80,9 +80,6 @@
     <t>D1, D2</t>
   </si>
   <si>
-    <t>J1</t>
-  </si>
-  <si>
     <t>P1</t>
   </si>
   <si>
@@ -125,9 +122,6 @@
     <t>100V -55℃~+150℃@(Tj) 400mW Single 1.25V@150mA 4ns 1μA@75V 200mA SOD-323 Switching Diode ROHS</t>
   </si>
   <si>
-    <t>CONN FFC BOTTOM 6POS 0.50MM R/A</t>
-  </si>
-  <si>
     <t>Sensor Connecting Pads</t>
   </si>
   <si>
@@ -164,9 +158,6 @@
     <t>SOD-323</t>
   </si>
   <si>
-    <t>FH19C-6S-0.5SH(10)</t>
-  </si>
-  <si>
     <t>sEMG sensor</t>
   </si>
   <si>
@@ -227,9 +218,6 @@
     <t>YFW</t>
   </si>
   <si>
-    <t>Hirose</t>
-  </si>
-  <si>
     <t>FH</t>
   </si>
   <si>
@@ -272,10 +260,34 @@
     <t>RC-02W8062FT</t>
   </si>
   <si>
-    <t>Quantity Per Board</t>
-  </si>
-  <si>
     <t>Quantity 40 Board</t>
+  </si>
+  <si>
+    <t>-------</t>
+  </si>
+  <si>
+    <t>100K</t>
+  </si>
+  <si>
+    <t>P9</t>
+  </si>
+  <si>
+    <t>Ribbon wire Connection Pads</t>
+  </si>
+  <si>
+    <t>Custom</t>
+  </si>
+  <si>
+    <t>6 pin Ribbon Pads.</t>
+  </si>
+  <si>
+    <t>Remarks</t>
+  </si>
+  <si>
+    <t>Do Not Mount</t>
+  </si>
+  <si>
+    <t>Quantity (1 Board)</t>
   </si>
 </sst>
 </file>
@@ -285,7 +297,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="[$-409]h:mm:ss\ AM/PM;@"/>
   </numFmts>
-  <fonts count="18" x14ac:knownFonts="1">
+  <fonts count="21" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -297,6 +309,7 @@
       <sz val="10"/>
       <color indexed="13"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
@@ -404,6 +417,30 @@
     </font>
     <font>
       <sz val="9"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <strike/>
+      <sz val="9"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <strike/>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -441,7 +478,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="17">
+  <borders count="21">
     <border>
       <left/>
       <right/>
@@ -623,11 +660,61 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="50">
+  <cellXfs count="70">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
@@ -747,6 +834,59 @@
     <xf numFmtId="0" fontId="17" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="2" borderId="14" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="4" borderId="20" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="4" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="2" borderId="14" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="2" borderId="5" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="4" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="4" borderId="14" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="4" borderId="5" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -755,6 +895,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -781,25 +927,20 @@
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:twoCellAnchor editAs="oneCell">
+  <xdr:oneCellAnchor>
     <xdr:from>
-      <xdr:col>9</xdr:col>
+      <xdr:col>10</xdr:col>
       <xdr:colOff>47625</xdr:colOff>
       <xdr:row>2</xdr:row>
       <xdr:rowOff>10417</xdr:rowOff>
     </xdr:from>
-    <xdr:to>
-      <xdr:col>9</xdr:col>
-      <xdr:colOff>1905000</xdr:colOff>
-      <xdr:row>7</xdr:row>
-      <xdr:rowOff>161925</xdr:rowOff>
-    </xdr:to>
+    <xdr:ext cx="1857375" cy="1104008"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="Picture 1">
+        <xdr:cNvPr id="3" name="Picture 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{27D43159-27D4-405D-B8BD-6C83466D09B4}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -829,7 +970,7 @@
       </xdr:spPr>
     </xdr:pic>
     <xdr:clientData/>
-  </xdr:twoCellAnchor>
+  </xdr:oneCellAnchor>
 </xdr:wsDr>
 </file>
 
@@ -1097,7 +1238,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:J25"/>
+  <dimension ref="A1:K25"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="3.140625" style="25" customWidth="1"/>
@@ -1107,10 +1248,10 @@
     <col min="6" max="6" width="33.42578125" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="21.42578125" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="29.42578125" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="29.42578125" customWidth="1"/>
+    <col min="9" max="11" width="29.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1"/>
       <c r="B1" s="19"/>
       <c r="C1" s="2"/>
@@ -1118,11 +1259,11 @@
       <c r="E1" s="2"/>
       <c r="F1" s="2"/>
       <c r="G1" s="2"/>
-      <c r="H1" s="47"/>
-      <c r="I1" s="47"/>
-      <c r="J1" s="47"/>
-    </row>
-    <row r="2" spans="1:10" ht="32.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="H1" s="65"/>
+      <c r="I1" s="65"/>
+      <c r="J1" s="65"/>
+    </row>
+    <row r="2" spans="1:11" ht="32.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1"/>
       <c r="B2" s="20"/>
       <c r="C2" s="10" t="s">
@@ -1136,9 +1277,10 @@
       <c r="G2" s="3"/>
       <c r="H2" s="3"/>
       <c r="I2" s="3"/>
-      <c r="J2" s="3"/>
-    </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J2" s="68"/>
+      <c r="K2" s="69"/>
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A3" s="1"/>
       <c r="B3" s="21"/>
       <c r="C3" s="12" t="s">
@@ -1152,9 +1294,10 @@
       <c r="G3" s="4"/>
       <c r="H3" s="4"/>
       <c r="I3" s="4"/>
-      <c r="J3" s="48"/>
-    </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J3" s="4"/>
+      <c r="K3" s="66"/>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A4" s="1"/>
       <c r="B4" s="21"/>
       <c r="C4" s="12" t="s">
@@ -1168,9 +1311,10 @@
       <c r="G4" s="6"/>
       <c r="H4" s="6"/>
       <c r="I4" s="6"/>
-      <c r="J4" s="49"/>
-    </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J4" s="6"/>
+      <c r="K4" s="67"/>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A5" s="1"/>
       <c r="B5" s="21"/>
       <c r="C5" s="12" t="s">
@@ -1184,9 +1328,10 @@
       <c r="G5" s="5"/>
       <c r="H5" s="5"/>
       <c r="I5" s="5"/>
-      <c r="J5" s="49"/>
-    </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J5" s="5"/>
+      <c r="K5" s="67"/>
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A6" s="1"/>
       <c r="B6" s="22"/>
       <c r="C6" s="15"/>
@@ -1196,9 +1341,10 @@
       <c r="G6" s="5"/>
       <c r="H6" s="5"/>
       <c r="I6" s="5"/>
-      <c r="J6" s="49"/>
-    </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J6" s="5"/>
+      <c r="K6" s="67"/>
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A7" s="1"/>
       <c r="B7" s="23"/>
       <c r="C7" s="17"/>
@@ -1208,9 +1354,10 @@
       <c r="G7" s="7"/>
       <c r="H7" s="7"/>
       <c r="I7" s="7"/>
-      <c r="J7" s="49"/>
-    </row>
-    <row r="8" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="J7" s="7"/>
+      <c r="K7" s="67"/>
+    </row>
+    <row r="8" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="1"/>
       <c r="B8" s="26"/>
       <c r="C8" s="27"/>
@@ -1220,9 +1367,10 @@
       <c r="G8" s="7"/>
       <c r="H8" s="7"/>
       <c r="I8" s="7"/>
-      <c r="J8" s="49"/>
-    </row>
-    <row r="9" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="J8" s="7"/>
+      <c r="K8" s="67"/>
+    </row>
+    <row r="9" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9" s="1"/>
       <c r="B9" s="29" t="s">
         <v>4</v>
@@ -1231,28 +1379,31 @@
         <v>10</v>
       </c>
       <c r="D9" s="30" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E9" s="29" t="s">
-        <v>40</v>
-      </c>
-      <c r="F9" s="30" t="s">
-        <v>50</v>
-      </c>
-      <c r="G9" s="29" t="s">
-        <v>60</v>
-      </c>
-      <c r="H9" s="30" t="s">
-        <v>70</v>
+        <v>38</v>
+      </c>
+      <c r="F9" s="29" t="s">
+        <v>47</v>
+      </c>
+      <c r="G9" s="30" t="s">
+        <v>57</v>
+      </c>
+      <c r="H9" s="29" t="s">
+        <v>66</v>
       </c>
       <c r="I9" s="29" t="s">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="J9" s="29" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="10" spans="1:10" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>76</v>
+      </c>
+      <c r="K9" s="29" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A10" s="1"/>
       <c r="B10" s="31">
         <f>ROW(B10) - ROW($B$9)</f>
@@ -1262,19 +1413,19 @@
         <v>11</v>
       </c>
       <c r="D10" s="38" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E10" s="37" t="s">
-        <v>41</v>
-      </c>
-      <c r="F10" s="38" t="s">
-        <v>51</v>
-      </c>
-      <c r="G10" s="37" t="s">
-        <v>61</v>
-      </c>
-      <c r="H10" s="38" t="s">
-        <v>71</v>
+        <v>39</v>
+      </c>
+      <c r="F10" s="37" t="s">
+        <v>48</v>
+      </c>
+      <c r="G10" s="38" t="s">
+        <v>58</v>
+      </c>
+      <c r="H10" s="37" t="s">
+        <v>67</v>
       </c>
       <c r="I10" s="37">
         <v>1</v>
@@ -1283,8 +1434,9 @@
         <f>I10*40</f>
         <v>40</v>
       </c>
-    </row>
-    <row r="11" spans="1:10" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="K10" s="41"/>
+    </row>
+    <row r="11" spans="1:11" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A11" s="1"/>
       <c r="B11" s="31">
         <f t="shared" ref="B11:B23" si="0">ROW(B11) - ROW($B$9)</f>
@@ -1294,19 +1446,19 @@
         <v>12</v>
       </c>
       <c r="D11" s="40" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E11" s="39" t="s">
-        <v>42</v>
-      </c>
-      <c r="F11" s="40" t="s">
-        <v>52</v>
-      </c>
-      <c r="G11" s="39" t="s">
-        <v>62</v>
-      </c>
-      <c r="H11" s="40" t="s">
-        <v>72</v>
+        <v>40</v>
+      </c>
+      <c r="F11" s="39" t="s">
+        <v>49</v>
+      </c>
+      <c r="G11" s="40" t="s">
+        <v>59</v>
+      </c>
+      <c r="H11" s="39" t="s">
+        <v>68</v>
       </c>
       <c r="I11" s="39">
         <v>1</v>
@@ -1315,26 +1467,27 @@
         <f t="shared" ref="J11:J23" si="1">I11*40</f>
         <v>40</v>
       </c>
-    </row>
-    <row r="12" spans="1:10" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="K11" s="46"/>
+    </row>
+    <row r="12" spans="1:11" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A12" s="1"/>
       <c r="B12" s="31">
-        <f>ROW(B12) - ROW($B$9)</f>
+        <f t="shared" si="0"/>
         <v>3</v>
       </c>
       <c r="C12" s="37" t="s">
         <v>13</v>
       </c>
       <c r="D12" s="38" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E12" s="37" t="s">
-        <v>42</v>
-      </c>
-      <c r="F12" s="38"/>
-      <c r="G12" s="37"/>
-      <c r="H12" s="38" t="s">
-        <v>73</v>
+        <v>40</v>
+      </c>
+      <c r="F12" s="37"/>
+      <c r="G12" s="38"/>
+      <c r="H12" s="37" t="s">
+        <v>69</v>
       </c>
       <c r="I12" s="37">
         <v>1</v>
@@ -1343,8 +1496,9 @@
         <f t="shared" si="1"/>
         <v>40</v>
       </c>
-    </row>
-    <row r="13" spans="1:10" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="K12" s="41"/>
+    </row>
+    <row r="13" spans="1:11" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A13" s="1"/>
       <c r="B13" s="31">
         <f t="shared" si="0"/>
@@ -1354,19 +1508,19 @@
         <v>14</v>
       </c>
       <c r="D13" s="40" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E13" s="39" t="s">
-        <v>42</v>
-      </c>
-      <c r="F13" s="40" t="s">
-        <v>53</v>
-      </c>
-      <c r="G13" s="39" t="s">
-        <v>63</v>
-      </c>
-      <c r="H13" s="40" t="s">
-        <v>74</v>
+        <v>40</v>
+      </c>
+      <c r="F13" s="39" t="s">
+        <v>50</v>
+      </c>
+      <c r="G13" s="40" t="s">
+        <v>60</v>
+      </c>
+      <c r="H13" s="39" t="s">
+        <v>70</v>
       </c>
       <c r="I13" s="39">
         <v>1</v>
@@ -1375,30 +1529,31 @@
         <f t="shared" si="1"/>
         <v>40</v>
       </c>
-    </row>
-    <row r="14" spans="1:10" ht="72.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="K13" s="46"/>
+    </row>
+    <row r="14" spans="1:11" ht="72.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A14" s="1"/>
       <c r="B14" s="31">
-        <f>ROW(B14) - ROW($B$9)</f>
+        <f t="shared" si="0"/>
         <v>5</v>
       </c>
       <c r="C14" s="37" t="s">
         <v>15</v>
       </c>
       <c r="D14" s="38" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E14" s="37" t="s">
-        <v>43</v>
-      </c>
-      <c r="F14" s="38" t="s">
-        <v>54</v>
-      </c>
-      <c r="G14" s="37" t="s">
-        <v>64</v>
-      </c>
-      <c r="H14" s="38" t="s">
-        <v>54</v>
+        <v>41</v>
+      </c>
+      <c r="F14" s="37" t="s">
+        <v>51</v>
+      </c>
+      <c r="G14" s="38" t="s">
+        <v>61</v>
+      </c>
+      <c r="H14" s="49" t="s">
+        <v>77</v>
       </c>
       <c r="I14" s="37">
         <v>2</v>
@@ -1407,90 +1562,101 @@
         <f t="shared" si="1"/>
         <v>80</v>
       </c>
-    </row>
-    <row r="15" spans="1:10" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="K14" s="41"/>
+    </row>
+    <row r="15" spans="1:11" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A15" s="1"/>
       <c r="B15" s="31">
         <f t="shared" si="0"/>
         <v>6</v>
       </c>
-      <c r="C15" s="39" t="s">
+      <c r="C15" s="59" t="s">
         <v>16</v>
       </c>
-      <c r="D15" s="40" t="s">
-        <v>31</v>
-      </c>
-      <c r="E15" s="39" t="s">
-        <v>44</v>
-      </c>
-      <c r="F15" s="40" t="s">
-        <v>44</v>
-      </c>
-      <c r="G15" s="39" t="s">
-        <v>65</v>
-      </c>
-      <c r="H15" s="40" t="s">
-        <v>44</v>
-      </c>
-      <c r="I15" s="39">
+      <c r="D15" s="60" t="s">
+        <v>30</v>
+      </c>
+      <c r="E15" s="59" t="s">
+        <v>42</v>
+      </c>
+      <c r="F15" s="61" t="s">
+        <v>77</v>
+      </c>
+      <c r="G15" s="62" t="s">
+        <v>77</v>
+      </c>
+      <c r="H15" s="61" t="s">
+        <v>77</v>
+      </c>
+      <c r="I15" s="59">
         <v>1</v>
       </c>
-      <c r="J15" s="46">
+      <c r="J15" s="63">
         <f t="shared" si="1"/>
         <v>40</v>
       </c>
-    </row>
-    <row r="16" spans="1:10" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="K15" s="64" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A16" s="1"/>
       <c r="B16" s="31">
-        <f>ROW(B16) - ROW($B$9)</f>
+        <f t="shared" si="0"/>
         <v>7</v>
       </c>
-      <c r="C16" s="37" t="s">
-        <v>17</v>
-      </c>
-      <c r="D16" s="38" t="s">
-        <v>32</v>
-      </c>
-      <c r="E16" s="37" t="s">
-        <v>45</v>
-      </c>
-      <c r="F16" s="38"/>
-      <c r="G16" s="37"/>
-      <c r="H16" s="38" t="s">
-        <v>45</v>
-      </c>
-      <c r="I16" s="37">
+      <c r="C16" s="53" t="s">
+        <v>79</v>
+      </c>
+      <c r="D16" s="54" t="s">
+        <v>80</v>
+      </c>
+      <c r="E16" s="58" t="s">
+        <v>81</v>
+      </c>
+      <c r="F16" s="53" t="s">
+        <v>82</v>
+      </c>
+      <c r="G16" s="56" t="s">
+        <v>77</v>
+      </c>
+      <c r="H16" s="55" t="s">
+        <v>77</v>
+      </c>
+      <c r="I16" s="53">
         <v>1</v>
       </c>
-      <c r="J16" s="41">
+      <c r="J16" s="57">
         <f t="shared" si="1"/>
         <v>40</v>
       </c>
-    </row>
-    <row r="17" spans="1:10" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="K16" s="52" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A17" s="1"/>
       <c r="B17" s="31">
         <f t="shared" si="0"/>
         <v>8</v>
       </c>
       <c r="C17" s="39" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D17" s="40" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="E17" s="39" t="s">
-        <v>46</v>
-      </c>
-      <c r="F17" s="40" t="s">
-        <v>55</v>
-      </c>
-      <c r="G17" s="39" t="s">
-        <v>63</v>
-      </c>
-      <c r="H17" s="40" t="s">
-        <v>75</v>
+        <v>43</v>
+      </c>
+      <c r="F17" s="39" t="s">
+        <v>52</v>
+      </c>
+      <c r="G17" s="40" t="s">
+        <v>60</v>
+      </c>
+      <c r="H17" s="39" t="s">
+        <v>71</v>
       </c>
       <c r="I17" s="39">
         <v>1</v>
@@ -1499,30 +1665,31 @@
         <f t="shared" si="1"/>
         <v>40</v>
       </c>
-    </row>
-    <row r="18" spans="1:10" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="K17" s="46"/>
+    </row>
+    <row r="18" spans="1:11" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A18" s="1"/>
       <c r="B18" s="31">
-        <f>ROW(B18) - ROW($B$9)</f>
+        <f t="shared" si="0"/>
         <v>9</v>
       </c>
       <c r="C18" s="37" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D18" s="38" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="E18" s="37" t="s">
-        <v>46</v>
-      </c>
-      <c r="F18" s="38" t="s">
-        <v>56</v>
-      </c>
-      <c r="G18" s="37" t="s">
-        <v>63</v>
-      </c>
-      <c r="H18" s="38" t="s">
-        <v>76</v>
+        <v>43</v>
+      </c>
+      <c r="F18" s="37" t="s">
+        <v>53</v>
+      </c>
+      <c r="G18" s="38" t="s">
+        <v>60</v>
+      </c>
+      <c r="H18" s="37" t="s">
+        <v>72</v>
       </c>
       <c r="I18" s="37">
         <v>5</v>
@@ -1531,30 +1698,31 @@
         <f t="shared" si="1"/>
         <v>200</v>
       </c>
-    </row>
-    <row r="19" spans="1:10" ht="60.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="K18" s="41"/>
+    </row>
+    <row r="19" spans="1:11" ht="60.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A19" s="1"/>
       <c r="B19" s="31">
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
       <c r="C19" s="39" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D19" s="40" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="E19" s="39" t="s">
-        <v>46</v>
-      </c>
-      <c r="F19" s="40" t="s">
-        <v>79</v>
-      </c>
-      <c r="G19" s="39" t="s">
-        <v>66</v>
-      </c>
-      <c r="H19" s="40" t="s">
-        <v>77</v>
+        <v>43</v>
+      </c>
+      <c r="F19" s="39" t="s">
+        <v>75</v>
+      </c>
+      <c r="G19" s="40" t="s">
+        <v>62</v>
+      </c>
+      <c r="H19" s="39" t="s">
+        <v>73</v>
       </c>
       <c r="I19" s="39">
         <v>2</v>
@@ -1563,30 +1731,31 @@
         <f t="shared" si="1"/>
         <v>80</v>
       </c>
-    </row>
-    <row r="20" spans="1:10" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="K19" s="46"/>
+    </row>
+    <row r="20" spans="1:11" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A20" s="1"/>
       <c r="B20" s="31">
-        <f>ROW(B20) - ROW($B$9)</f>
+        <f t="shared" si="0"/>
         <v>11</v>
       </c>
       <c r="C20" s="37" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D20" s="38" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="E20" s="37" t="s">
-        <v>47</v>
-      </c>
-      <c r="F20" s="38" t="s">
-        <v>47</v>
-      </c>
-      <c r="G20" s="37" t="s">
-        <v>67</v>
-      </c>
-      <c r="H20" s="38" t="s">
-        <v>47</v>
+        <v>44</v>
+      </c>
+      <c r="F20" s="37" t="s">
+        <v>44</v>
+      </c>
+      <c r="G20" s="38" t="s">
+        <v>63</v>
+      </c>
+      <c r="H20" s="49" t="s">
+        <v>78</v>
       </c>
       <c r="I20" s="37">
         <v>1</v>
@@ -1595,30 +1764,31 @@
         <f t="shared" si="1"/>
         <v>40</v>
       </c>
-    </row>
-    <row r="21" spans="1:10" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="K20" s="41"/>
+    </row>
+    <row r="21" spans="1:11" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A21" s="1"/>
       <c r="B21" s="31">
         <f t="shared" si="0"/>
         <v>12</v>
       </c>
       <c r="C21" s="39" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D21" s="40" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="E21" s="39" t="s">
-        <v>46</v>
-      </c>
-      <c r="F21" s="40" t="s">
-        <v>57</v>
-      </c>
-      <c r="G21" s="39" t="s">
-        <v>63</v>
-      </c>
-      <c r="H21" s="40" t="s">
-        <v>78</v>
+        <v>43</v>
+      </c>
+      <c r="F21" s="39" t="s">
+        <v>54</v>
+      </c>
+      <c r="G21" s="40" t="s">
+        <v>60</v>
+      </c>
+      <c r="H21" s="39" t="s">
+        <v>74</v>
       </c>
       <c r="I21" s="39">
         <v>1</v>
@@ -1627,30 +1797,31 @@
         <f t="shared" si="1"/>
         <v>40</v>
       </c>
-    </row>
-    <row r="22" spans="1:10" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="K21" s="46"/>
+    </row>
+    <row r="22" spans="1:11" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A22" s="1"/>
       <c r="B22" s="31">
-        <f>ROW(B22) - ROW($B$9)</f>
+        <f t="shared" si="0"/>
         <v>13</v>
       </c>
       <c r="C22" s="37" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D22" s="38" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="E22" s="37" t="s">
-        <v>48</v>
-      </c>
-      <c r="F22" s="38" t="s">
-        <v>58</v>
-      </c>
-      <c r="G22" s="37" t="s">
-        <v>68</v>
-      </c>
-      <c r="H22" s="38" t="s">
-        <v>58</v>
+        <v>45</v>
+      </c>
+      <c r="F22" s="37" t="s">
+        <v>55</v>
+      </c>
+      <c r="G22" s="38" t="s">
+        <v>64</v>
+      </c>
+      <c r="H22" s="49" t="s">
+        <v>77</v>
       </c>
       <c r="I22" s="37">
         <v>1</v>
@@ -1659,30 +1830,31 @@
         <f t="shared" si="1"/>
         <v>40</v>
       </c>
-    </row>
-    <row r="23" spans="1:10" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="K22" s="41"/>
+    </row>
+    <row r="23" spans="1:11" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A23" s="1"/>
       <c r="B23" s="31">
         <f t="shared" si="0"/>
         <v>14</v>
       </c>
       <c r="C23" s="39" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D23" s="40" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="E23" s="39" t="s">
-        <v>49</v>
-      </c>
-      <c r="F23" s="40" t="s">
-        <v>59</v>
-      </c>
-      <c r="G23" s="39" t="s">
-        <v>69</v>
-      </c>
-      <c r="H23" s="40" t="s">
-        <v>59</v>
+        <v>46</v>
+      </c>
+      <c r="F23" s="51" t="s">
+        <v>56</v>
+      </c>
+      <c r="G23" s="40" t="s">
+        <v>65</v>
+      </c>
+      <c r="H23" s="50" t="s">
+        <v>77</v>
       </c>
       <c r="I23" s="39">
         <v>1</v>
@@ -1691,8 +1863,9 @@
         <f t="shared" si="1"/>
         <v>40</v>
       </c>
-    </row>
-    <row r="24" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K23" s="46"/>
+    </row>
+    <row r="24" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A24" s="1"/>
       <c r="B24" s="32"/>
       <c r="C24" s="33" t="s">
@@ -1704,9 +1877,10 @@
       <c r="G24" s="35"/>
       <c r="H24" s="36"/>
       <c r="I24" s="36"/>
-      <c r="J24" s="36"/>
-    </row>
-    <row r="25" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="J24" s="47"/>
+      <c r="K24" s="47"/>
+    </row>
+    <row r="25" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A25" s="1"/>
       <c r="B25" s="24"/>
       <c r="C25" s="8" t="s">
@@ -1718,12 +1892,14 @@
       <c r="G25" s="9"/>
       <c r="H25" s="9"/>
       <c r="I25" s="9"/>
-      <c r="J25" s="9"/>
+      <c r="J25" s="48"/>
+      <c r="K25" s="48"/>
     </row>
   </sheetData>
-  <mergeCells count="2">
+  <mergeCells count="3">
     <mergeCell ref="H1:J1"/>
-    <mergeCell ref="J3:J8"/>
+    <mergeCell ref="K3:K8"/>
+    <mergeCell ref="J2:K2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
